--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487512_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487512_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6562</v>
+        <v>3.8513</v>
       </c>
       <c r="E2" t="n">
-        <v>1.0848</v>
+        <v>2.8145</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5714</v>
+        <v>1.0368</v>
       </c>
       <c r="G2" t="n">
         <v>-0.5644</v>
@@ -610,13 +610,13 @@
         <v>3.1336</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0835</v>
+        <v>1.2786</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.5268</v>
+        <v>0.2029</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6103</v>
+        <v>1.0757</v>
       </c>
       <c r="V2" t="n">
         <v>2.1578</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. GARCIA ORTIZ</t>
+          <t>A. IGLESIAS CAMINO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2421</v>
+        <v>1.8517</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4175</v>
+        <v>2.2984</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1754</v>
+        <v>-0.4467</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.9847</v>
+        <v>2.6472</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.5913</v>
+        <v>1.7332</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3934</v>
+        <v>0.914</v>
       </c>
       <c r="J3" t="n">
-        <v>1.513</v>
+        <v>6.2096</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5835</v>
+        <v>3.1591</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9295</v>
+        <v>3.0504</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.4978</v>
+        <v>-3.5624</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.1748</v>
+        <v>-1.4259</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.3229</v>
+        <v>-2.1364</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5668</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1751</v>
+        <v>-4.1128</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7419</v>
+        <v>2.1543</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9354</v>
+        <v>0.7725</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8042</v>
+        <v>0.2017</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1312</v>
+        <v>0.5708</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2754</v>
+        <v>0.3905</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5507</v>
+        <v>0.3905</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. PAZ VAZQUEZ</t>
+          <t>L. GARCIA ORTIZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6959</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1564</v>
+        <v>1.6943</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8522999999999999</v>
+        <v>-0.721</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1896</v>
+        <v>-1.9847</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6393</v>
+        <v>-1.5913</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4498</v>
+        <v>-0.3934</v>
       </c>
       <c r="J4" t="n">
-        <v>0.08119999999999999</v>
+        <v>1.513</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0408</v>
+        <v>0.5835</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0404</v>
+        <v>0.9295</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2708</v>
+        <v>-3.4978</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6802</v>
+        <v>-2.1748</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4093</v>
+        <v>-1.3229</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1958</v>
+        <v>1.5668</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1751</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1958</v>
+        <v>2.7419</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0238</v>
+        <v>1.6666</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2376</v>
+        <v>1.081</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2614</v>
+        <v>0.5856</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6659</v>
+        <v>-0.2754</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6659</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. IGLESIAS CAMINO</t>
+          <t>D. PAZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.064</v>
+        <v>0.7019</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6711</v>
+        <v>-0.097</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6071</v>
+        <v>0.7988</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6472</v>
+        <v>-0.1896</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7332</v>
+        <v>-0.6393</v>
       </c>
       <c r="I5" t="n">
-        <v>0.914</v>
+        <v>0.4498</v>
       </c>
       <c r="J5" t="n">
-        <v>6.2096</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1591</v>
+        <v>0.0408</v>
       </c>
       <c r="L5" t="n">
-        <v>3.0504</v>
+        <v>0.0404</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.5624</v>
+        <v>-0.2708</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4259</v>
+        <v>-0.6802</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.1364</v>
+        <v>0.4093</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.9585</v>
+        <v>0.1958</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.1128</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1543</v>
+        <v>0.1958</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0152</v>
+        <v>0.0297</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.4256</v>
+        <v>-0.1782</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4104</v>
+        <v>0.2079</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3905</v>
+        <v>0.6659</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3905</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4847</v>
+        <v>-1.1371</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8229</v>
+        <v>-1.5822</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3382</v>
+        <v>0.4451</v>
       </c>
       <c r="G6" t="n">
         <v>-2.1717</v>
@@ -922,13 +922,13 @@
         <v>1.3709</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0199</v>
+        <v>0.3676</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9069</v>
+        <v>0.1476</v>
       </c>
       <c r="U6" t="n">
-        <v>0.113</v>
+        <v>0.22</v>
       </c>
       <c r="V6" t="n">
         <v>0.2754</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3346</v>
+        <v>-1.2868</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.9258</v>
+        <v>-3.0116</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5912</v>
+        <v>1.7248</v>
       </c>
       <c r="G7" t="n">
         <v>-2.1982</v>
@@ -1000,13 +1000,13 @@
         <v>1.5668</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5514</v>
+        <v>0.5992</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0129</v>
+        <v>-0.0988</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5643</v>
+        <v>0.698</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2754</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. GIL REY</t>
+          <t>J. HERMO ANTELO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8045</v>
+        <v>-1.5763</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7741</v>
+        <v>-0.5555</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0304</v>
+        <v>-1.0208</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.341</v>
+        <v>-1.7216</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9053</v>
+        <v>-0.231</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.4356</v>
+        <v>-1.4905</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1755</v>
+        <v>-0.6414</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5883</v>
+        <v>0.0408</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.7638</v>
+        <v>-0.6822</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.1655</v>
+        <v>-1.0802</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4936</v>
+        <v>-0.2719</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.6718</v>
+        <v>-0.8083</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1543</v>
+        <v>0.1958</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1751</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.3294</v>
+        <v>0.1958</v>
       </c>
       <c r="S8" t="n">
-        <v>2.1056</v>
+        <v>-0.0506</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0833</v>
+        <v>0.0859</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0222</v>
+        <v>-0.1364</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7235</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4931</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. HERMO ANTELO</t>
+          <t>L. GARCÍA SINDIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8998</v>
+        <v>-1.9218</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.879</v>
+        <v>-0.9792999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0208</v>
+        <v>-0.9424</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7216</v>
+        <v>-2.2452</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.231</v>
+        <v>-1.9823</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4905</v>
+        <v>-0.2629</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6414</v>
+        <v>-0.7682</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0408</v>
+        <v>-1.3032</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6822</v>
+        <v>0.535</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0802</v>
+        <v>-1.477</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2719</v>
+        <v>-0.6791</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8083</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1958</v>
+        <v>0.3917</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1958</v>
+        <v>0.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3741</v>
+        <v>-0.0682</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2376</v>
+        <v>-0.2111</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1364</v>
+        <v>0.1429</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. GARCÍA SINDIN</t>
+          <t>C. GIL REY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0789</v>
+        <v>-2.0994</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2434</v>
+        <v>-0.9888</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8355</v>
+        <v>-1.1106</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.2452</v>
+        <v>-5.341</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9823</v>
+        <v>-0.9053</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2629</v>
+        <v>-4.4356</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7682</v>
+        <v>-1.1755</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3032</v>
+        <v>0.5883</v>
       </c>
       <c r="L10" t="n">
-        <v>0.535</v>
+        <v>-1.7638</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.477</v>
+        <v>-4.1655</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6791</v>
+        <v>-1.4936</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-2.6718</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3917</v>
+        <v>2.1543</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1751</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3917</v>
+        <v>3.3294</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2254</v>
+        <v>1.8107</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4752</v>
+        <v>0.8687</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2498</v>
+        <v>0.9421</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.7235</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.4931</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.0794</v>
+        <v>-6.5985</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.5817</v>
+        <v>-5.0206</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4977</v>
+        <v>-1.5779</v>
       </c>
       <c r="G11" t="n">
         <v>-5.2555</v>
@@ -1312,13 +1312,13 @@
         <v>2.546</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4088</v>
+        <v>0.8897</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0612</v>
+        <v>0.4999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.47</v>
+        <v>0.3898</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6659</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.023699999999998</v>
+        <v>-7.241699999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.2099</v>
+        <v>-5.4278</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8138</v>
+        <v>-1.8139</v>
       </c>
       <c r="G12" t="n">
         <v>-19.0247</v>
@@ -1390,22 +1390,22 @@
         <v>17.6262</v>
       </c>
       <c r="S12" t="n">
-        <v>5.5137</v>
+        <v>7.2958</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8174999999999998</v>
+        <v>2.5996</v>
       </c>
       <c r="U12" t="n">
-        <v>4.696199999999999</v>
+        <v>4.6964</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5494</v>
+        <v>1.549399999999999</v>
       </c>
       <c r="W12" t="n">
         <v>2.1454</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5957999999999998</v>
+        <v>-0.5957999999999997</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.5264</v>
+        <v>7.1127</v>
       </c>
       <c r="E13" t="n">
-        <v>4.6786</v>
+        <v>4.781</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8477</v>
+        <v>2.3317</v>
       </c>
       <c r="G13" t="n">
         <v>6.5831</v>
@@ -1468,13 +1468,13 @@
         <v>1.9585</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5486</v>
+        <v>-0.9623</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8734</v>
+        <v>-0.7711</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6752</v>
+        <v>-0.1913</v>
       </c>
       <c r="V13" t="n">
         <v>1.492</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. PEREZ MARTIN</t>
+          <t>F. SALVADORES ALVAREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3728</v>
+        <v>3.6226</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5149</v>
+        <v>4.0968</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8579</v>
+        <v>-0.4741</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5759</v>
+        <v>3.609</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0163</v>
+        <v>2.3917</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5921</v>
+        <v>1.2173</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8218</v>
+        <v>5.4048</v>
       </c>
       <c r="K14" t="n">
-        <v>0.114</v>
+        <v>2.3188</v>
       </c>
       <c r="L14" t="n">
-        <v>2.7078</v>
+        <v>3.086</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2459</v>
+        <v>-1.7958</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1302</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1157</v>
+        <v>-1.8687</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.5875</v>
+        <v>0.5875</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3709</v>
+        <v>1.5668</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7186</v>
+        <v>-0.5739</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6516</v>
+        <v>-0.3288</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0669</v>
+        <v>-0.2451</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6659</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. SALVADORES ALVAREZ</t>
+          <t>R. PEREZ MARTIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9147</v>
+        <v>2.4472</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7898</v>
+        <v>0.6962</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8751</v>
+        <v>1.751</v>
       </c>
       <c r="G15" t="n">
-        <v>3.609</v>
+        <v>2.5759</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3917</v>
+        <v>-0.0163</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2173</v>
+        <v>2.5921</v>
       </c>
       <c r="J15" t="n">
-        <v>5.4048</v>
+        <v>2.8218</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3188</v>
+        <v>0.114</v>
       </c>
       <c r="L15" t="n">
-        <v>3.086</v>
+        <v>2.7078</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7958</v>
+        <v>-0.2459</v>
       </c>
       <c r="N15" t="n">
-        <v>0.07290000000000001</v>
+        <v>-0.1302</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.8687</v>
+        <v>-0.1157</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5875</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5668</v>
+        <v>1.3709</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2818</v>
+        <v>-0.207</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6358</v>
+        <v>-0.167</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6461</v>
+        <v>-0.04</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7767</v>
+        <v>2.198</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2963</v>
+        <v>0.5009</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4804</v>
+        <v>1.6971</v>
       </c>
       <c r="G16" t="n">
         <v>1.6131</v>
@@ -1702,13 +1702,13 @@
         <v>2.3502</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4827</v>
+        <v>-1.0614</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.188</v>
+        <v>-0.9834000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2947</v>
+        <v>-0.0781</v>
       </c>
       <c r="V16" t="n">
         <v>0.2754</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4882</v>
+        <v>1.5582</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0097</v>
+        <v>-0.3167</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4979</v>
+        <v>1.8749</v>
       </c>
       <c r="G17" t="n">
         <v>2.1148</v>
@@ -1780,13 +1780,13 @@
         <v>1.7626</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.546</v>
+        <v>-0.4759</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1494</v>
+        <v>-0.4564</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3966</v>
+        <v>-0.0196</v>
       </c>
       <c r="V17" t="n">
         <v>0.1152</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.009</v>
+        <v>0.9288</v>
       </c>
       <c r="E18" t="n">
         <v>0.8516</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1574</v>
+        <v>0.0772</v>
       </c>
       <c r="G18" t="n">
         <v>0.1766</v>
@@ -1858,13 +1858,13 @@
         <v>0.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2252</v>
+        <v>-0.3054</v>
       </c>
       <c r="T18" t="n">
         <v>0.077</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3022</v>
+        <v>-0.3824</v>
       </c>
       <c r="V18" t="n">
         <v>0.6659</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3873</v>
+        <v>-0.2583</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8343</v>
+        <v>-0.732</v>
       </c>
       <c r="F19" t="n">
-        <v>0.447</v>
+        <v>0.4737</v>
       </c>
       <c r="G19" t="n">
         <v>-0.605</v>
@@ -1936,13 +1936,13 @@
         <v>0.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2904</v>
+        <v>-0.1613</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4158</v>
+        <v>-0.3135</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1255</v>
+        <v>0.1522</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2754</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8387</v>
+        <v>-2.7649</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5298</v>
+        <v>-1.3251</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.309</v>
+        <v>-1.4399</v>
       </c>
       <c r="G20" t="n">
         <v>0.4609</v>
@@ -2014,13 +2014,13 @@
         <v>2.546</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7881</v>
+        <v>-0.7143</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2892</v>
+        <v>-1.0845</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5011</v>
+        <v>0.3702</v>
       </c>
       <c r="V20" t="n">
         <v>-3.0991</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.8379</v>
+        <v>-5.1384</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.9436</v>
+        <v>-6.739</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1057</v>
+        <v>1.6006</v>
       </c>
       <c r="G21" t="n">
         <v>2.4964</v>
@@ -2092,13 +2092,13 @@
         <v>1.9585</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.3699</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8734</v>
+        <v>-0.6687</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8038999999999999</v>
+        <v>0.2988</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3894</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>9.023900000000001</v>
+        <v>9.7059</v>
       </c>
       <c r="E22" t="n">
-        <v>1.813800000000001</v>
+        <v>1.813700000000002</v>
       </c>
       <c r="F22" t="n">
-        <v>7.209900000000001</v>
+        <v>7.8922</v>
       </c>
       <c r="G22" t="n">
         <v>19.0248</v>
@@ -2161,7 +2161,7 @@
         <v>-3.2036</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.937799999999999</v>
+        <v>-2.9378</v>
       </c>
       <c r="Q22" t="n">
         <v>-17.6264</v>
@@ -2170,13 +2170,13 @@
         <v>14.6886</v>
       </c>
       <c r="S22" t="n">
-        <v>-5.5137</v>
+        <v>-4.8314</v>
       </c>
       <c r="T22" t="n">
-        <v>-4.6964</v>
+        <v>-4.696400000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8174000000000002</v>
+        <v>-0.1353</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5495</v>
